--- a/generalist/web/public/resources/exit-cgt/badr-exit-model.xlsx
+++ b/generalist/web/public/resources/exit-cgt/badr-exit-model.xlsx
@@ -140,7 +140,7 @@
     <t>Assumptions and limitations</t>
   </si>
   <si>
-    <t>• BADR (Business Asset Disposal Relief): 14% on qualifying gains up to a £1m lifetime</t>
+    <t>• BADR (Business Asset Disposal Relief): 18% from 6 April 2026 (14% in 2025/26) on qualifying gains up to a £1m lifetime</t>
   </si>
   <si>
     <t xml:space="preserve">  limit for disposals to 5 April 2026; 18% from 6 April 2026. Gains above the limit</t>
